--- a/output/graficos_dimensiones/comunal_e_basneta_a_2024_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basneta_a_2024_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 00:05</t>
+    <t xml:space="preserve">2026-08-17 15:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_basneta_a_2024_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basneta_a_2024_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 15:03</t>
+    <t xml:space="preserve">2026-08-17 17:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_basneta_a_2024_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basneta_a_2024_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 17:47</t>
+    <t xml:space="preserve">2026-09-06 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
